--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1938,15 +1938,15 @@
   <dimension ref="A1:AN68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.28515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.0390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.48828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.99609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1957,26 +1957,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="138.09375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="37.0390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.41015625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="47.47265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="148.83203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="125.08984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="47.84375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="148.43359375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="125.03125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於針對第四級健康管理勞工，由醫師、事業單位等共同制定之適性配工計畫（變更場所、工作或縮短工時等），繼承自 TW Core CarePlan。</t>
+    <t>【依據：勞工健康保護規則附表】用於針對第四級健康管理勞工，由醫師、事業單位等共同制定之適性配工計畫（變更場所、工作或縮短工時等），繼承自 TW Core CarePlan。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -554,7 +554,7 @@
     <t>適性配工建議項目擴充</t>
   </si>
   <si>
-    <t>用於 CarePlan 中標註具體的適性配工或變更作業場所等建議項目。</t>
+    <t>【依據：勞工健康保護規則附表】用於 CarePlan 中標註具體的適性配工或變更作業場所等建議項目。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>指出計畫是否正在實施、代表未來意圖或是現在的歷史記錄。</t>
+  </si>
+  <si>
+    <t>active</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-status</t>
@@ -4425,7 +4428,7 @@
         <v>22</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>22</v>
@@ -4446,7 +4449,7 @@
         <v>221</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>22</v>
@@ -4479,24 +4482,24 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4522,16 +4525,16 @@
         <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>22</v>
@@ -4541,7 +4544,7 @@
         <v>22</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>22</v>
@@ -4559,10 +4562,10 @@
         <v>145</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>22</v>
@@ -4580,7 +4583,7 @@
         <v>22</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>88</v>
@@ -4595,7 +4598,7 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>22</v>
@@ -4609,10 +4612,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4635,19 +4638,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>22</v>
@@ -4672,19 +4675,19 @@
         <v>22</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -4694,7 +4697,7 @@
         <v>139</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4715,7 +4718,7 @@
         <v>22</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>22</v>
@@ -4723,13 +4726,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>22</v>
@@ -4751,19 +4754,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>22</v>
@@ -4773,7 +4776,7 @@
         <v>22</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>22</v>
@@ -4788,13 +4791,13 @@
         <v>22</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>22</v>
@@ -4812,7 +4815,7 @@
         <v>22</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4833,7 +4836,7 @@
         <v>22</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>22</v>
@@ -4841,10 +4844,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4870,10 +4873,10 @@
         <v>126</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4924,7 +4927,7 @@
         <v>22</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4953,10 +4956,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4982,14 +4985,14 @@
         <v>126</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>22</v>
@@ -5038,7 +5041,7 @@
         <v>22</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5059,7 +5062,7 @@
         <v>22</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>22</v>
@@ -5067,14 +5070,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5093,17 +5096,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>22</v>
@@ -5152,7 +5155,7 @@
         <v>22</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -5167,24 +5170,24 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5207,16 +5210,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5266,7 +5269,7 @@
         <v>22</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5281,28 +5284,28 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5321,19 +5324,19 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>22</v>
@@ -5382,7 +5385,7 @@
         <v>22</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5397,28 +5400,28 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5437,13 +5440,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5494,7 +5497,7 @@
         <v>22</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5509,13 +5512,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>22</v>
@@ -5523,10 +5526,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5549,13 +5552,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>205</v>
@@ -5608,7 +5611,7 @@
         <v>22</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5623,13 +5626,13 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>22</v>
@@ -5637,10 +5640,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5663,13 +5666,13 @@
         <v>22</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>205</v>
@@ -5722,7 +5725,7 @@
         <v>22</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5751,10 +5754,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5777,19 +5780,19 @@
         <v>22</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>205</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>22</v>
@@ -5838,7 +5841,7 @@
         <v>22</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5853,13 +5856,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>22</v>
@@ -5867,10 +5870,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5893,19 +5896,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>205</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>22</v>
@@ -5954,7 +5957,7 @@
         <v>22</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5969,24 +5972,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6009,19 +6012,19 @@
         <v>22</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>22</v>
@@ -6070,7 +6073,7 @@
         <v>22</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6085,7 +6088,7 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>22</v>
@@ -6099,10 +6102,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6125,19 +6128,19 @@
         <v>22</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>22</v>
@@ -6186,7 +6189,7 @@
         <v>22</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6204,21 +6207,21 @@
         <v>22</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6241,17 +6244,17 @@
         <v>22</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>22</v>
@@ -6300,7 +6303,7 @@
         <v>22</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6312,13 +6315,13 @@
         <v>22</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>22</v>
@@ -6329,10 +6332,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6441,10 +6444,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6555,14 +6558,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6584,10 +6587,10 @@
         <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>136</v>
@@ -6642,7 +6645,7 @@
         <v>22</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6671,10 +6674,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6697,16 +6700,16 @@
         <v>22</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6732,13 +6735,13 @@
         <v>22</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>22</v>
@@ -6756,7 +6759,7 @@
         <v>22</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6785,10 +6788,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6811,19 +6814,19 @@
         <v>22</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>22</v>
@@ -6872,7 +6875,7 @@
         <v>22</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6887,10 +6890,10 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>22</v>
@@ -6901,10 +6904,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6927,19 +6930,19 @@
         <v>22</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>22</v>
@@ -6988,7 +6991,7 @@
         <v>22</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7006,21 +7009,21 @@
         <v>22</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7043,19 +7046,19 @@
         <v>22</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>205</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>22</v>
@@ -7104,7 +7107,7 @@
         <v>22</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7113,16 +7116,16 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>22</v>
@@ -7133,10 +7136,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7159,17 +7162,17 @@
         <v>22</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>22</v>
@@ -7218,7 +7221,7 @@
         <v>22</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7227,7 +7230,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -7236,7 +7239,7 @@
         <v>22</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>22</v>
@@ -7247,10 +7250,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7359,10 +7362,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7473,14 +7476,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7502,10 +7505,10 @@
         <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>136</v>
@@ -7560,7 +7563,7 @@
         <v>22</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7589,10 +7592,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7618,14 +7621,14 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>22</v>
@@ -7653,10 +7656,10 @@
         <v>145</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>22</v>
@@ -7674,7 +7677,7 @@
         <v>22</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7692,7 +7695,7 @@
         <v>22</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>22</v>
@@ -7703,10 +7706,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7729,17 +7732,17 @@
         <v>22</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>191</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>22</v>
@@ -7788,7 +7791,7 @@
         <v>22</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7817,10 +7820,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7849,13 +7852,13 @@
         <v>196</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>198</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>22</v>
@@ -7904,7 +7907,7 @@
         <v>22</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7933,10 +7936,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7959,19 +7962,19 @@
         <v>22</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>22</v>
@@ -7996,13 +7999,13 @@
         <v>22</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>22</v>
@@ -8020,7 +8023,7 @@
         <v>22</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8035,24 +8038,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8075,16 +8078,16 @@
         <v>22</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8110,13 +8113,13 @@
         <v>22</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>22</v>
@@ -8134,7 +8137,7 @@
         <v>22</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8149,7 +8152,7 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>22</v>
@@ -8163,10 +8166,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8189,16 +8192,16 @@
         <v>22</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8248,7 +8251,7 @@
         <v>22</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8263,7 +8266,7 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>22</v>
@@ -8277,10 +8280,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8303,17 +8306,17 @@
         <v>22</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>22</v>
@@ -8362,7 +8365,7 @@
         <v>22</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8380,7 +8383,7 @@
         <v>22</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>22</v>
@@ -8391,10 +8394,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8420,16 +8423,16 @@
         <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>22</v>
@@ -8457,10 +8460,10 @@
         <v>145</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>22</v>
@@ -8478,7 +8481,7 @@
         <v>22</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>88</v>
@@ -8493,24 +8496,24 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8533,16 +8536,16 @@
         <v>22</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8592,7 +8595,7 @@
         <v>22</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8607,7 +8610,7 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>22</v>
@@ -8621,10 +8624,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8647,70 +8650,70 @@
         <v>22</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Q59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q59" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="R59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8725,10 +8728,10 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>22</v>
@@ -8739,10 +8742,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8765,17 +8768,17 @@
         <v>22</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>22</v>
@@ -8824,7 +8827,7 @@
         <v>22</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8839,24 +8842,24 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8879,19 +8882,19 @@
         <v>22</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>205</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>22</v>
@@ -8940,7 +8943,7 @@
         <v>22</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8958,21 +8961,21 @@
         <v>22</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8995,19 +8998,19 @@
         <v>22</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>205</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>22</v>
@@ -9056,7 +9059,7 @@
         <v>22</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9071,24 +9074,24 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9111,13 +9114,13 @@
         <v>22</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9144,19 +9147,19 @@
         <v>22</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
@@ -9166,7 +9169,7 @@
         <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9184,24 +9187,24 @@
         <v>22</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>22</v>
@@ -9223,13 +9226,13 @@
         <v>22</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>205</v>
@@ -9282,7 +9285,7 @@
         <v>22</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9300,25 +9303,25 @@
         <v>22</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9337,17 +9340,17 @@
         <v>22</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>22</v>
@@ -9396,7 +9399,7 @@
         <v>22</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9414,21 +9417,21 @@
         <v>22</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9451,13 +9454,13 @@
         <v>22</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9508,7 +9511,7 @@
         <v>22</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9526,21 +9529,21 @@
         <v>22</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9566,10 +9569,10 @@
         <v>126</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9620,7 +9623,7 @@
         <v>22</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9638,21 +9641,21 @@
         <v>22</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9675,17 +9678,17 @@
         <v>22</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>22</v>
@@ -9734,7 +9737,7 @@
         <v>22</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9749,16 +9752,16 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-CarePlan.xlsx
+++ b/StructureDefinition-TWHA-CarePlan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
